--- a/data/trans_orig/IP26B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP26B-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22835</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15506</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30289</t>
+          <t>30370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>22934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37951</t>
+          <t>37901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41677</t>
+          <t>42290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54180</t>
+          <t>53995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74743</t>
+          <t>74097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41236</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57649</t>
+          <t>57043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>40586</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56334</t>
+          <t>57150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>86346</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108759</t>
+          <t>108907</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>13017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10838</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>12626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>26502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36661</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33368</t>
+          <t>32608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46327</t>
+          <t>46109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66142</t>
+          <t>65527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29990</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45065</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32148</t>
+          <t>31917</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47361</t>
+          <t>46381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67115</t>
+          <t>66890</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88670</t>
+          <t>88000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23049</t>
+          <t>22941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>31429</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>24349</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38975</t>
+          <t>39429</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45235</t>
+          <t>46197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65292</t>
+          <t>66036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42239</t>
+          <t>42074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45779</t>
+          <t>46265</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62251</t>
+          <t>62475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>80414</t>
+          <t>79595</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>102113</t>
+          <t>101281</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>23910</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>20758</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>38560</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62886</t>
+          <t>61536</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84211</t>
+          <t>83391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>44661</t>
+          <t>44963</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66253</t>
+          <t>65960</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>111839</t>
+          <t>114374</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>142338</t>
+          <t>144533</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92050</t>
+          <t>92244</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113990</t>
+          <t>115205</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94769</t>
+          <t>94982</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>117593</t>
+          <t>118183</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>193973</t>
+          <t>193385</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>224953</t>
+          <t>225915</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11086</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>23602</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33930</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23167</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38622</t>
+          <t>39229</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>39325</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>56523</t>
+          <t>57014</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>66307</t>
+          <t>67400</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>89635</t>
+          <t>90136</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43420</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>59040</t>
+          <t>59462</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51448</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>69280</t>
+          <t>68827</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>99660</t>
+          <t>99522</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>124659</t>
+          <t>123256</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,4%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21759</t>
+          <t>20604</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>34876</t>
+          <t>34851</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>31172</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>44020</t>
+          <t>42657</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>61739</t>
+          <t>62576</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>29851</t>
+          <t>30089</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>43785</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>32592</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>45768</t>
+          <t>46086</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>65942</t>
+          <t>65934</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>85723</t>
+          <t>85795</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>41006</t>
+          <t>41970</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>65709</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>42324</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>64855</t>
+          <t>64858</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>90731</t>
+          <t>89318</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>122039</t>
+          <t>122213</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>197466</t>
+          <t>197437</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>237215</t>
+          <t>235038</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>198380</t>
+          <t>196830</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>235973</t>
+          <t>235977</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>406801</t>
+          <t>405176</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>463219</t>
+          <t>460121</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>293757</t>
+          <t>294839</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>335909</t>
+          <t>334579</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>327391</t>
+          <t>328852</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>369227</t>
+          <t>369309</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>632039</t>
+          <t>635535</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>692663</t>
+          <t>694092</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>52341</t>
+          <t>50182</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>56516</t>
+          <t>56678</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>72259</t>
+          <t>70904</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>100513</t>
+          <t>99971</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>26990</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>25035</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>43449</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>19844</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>16454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31486</t>
+          <t>31996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>48662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62915</t>
+          <t>62737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51291</t>
+          <t>51615</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66190</t>
+          <t>66596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103966</t>
+          <t>104625</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124893</t>
+          <t>125130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23363</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18033</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>18003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>36051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53920</t>
+          <t>54349</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69274</t>
+          <t>68955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>50057</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65345</t>
+          <t>65608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109419</t>
+          <t>109547</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129826</t>
+          <t>131145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17776</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>30656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>13198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19527</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>33028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45886</t>
+          <t>45381</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60890</t>
+          <t>60128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>43812</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57951</t>
+          <t>58621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95186</t>
+          <t>93838</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116250</t>
+          <t>115081</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28102</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19507</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20326</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>37246</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24178</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41951</t>
+          <t>40909</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37957</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50306</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74395</t>
+          <t>73789</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>110354</t>
+          <t>110696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134564</t>
+          <t>133633</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>128491</t>
+          <t>129585</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>152356</t>
+          <t>152815</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>245610</t>
+          <t>247442</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>279965</t>
+          <t>280428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,07%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24723</t>
+          <t>25040</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42717</t>
+          <t>42434</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>25108</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41310</t>
+          <t>41643</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53015</t>
+          <t>53979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>77827</t>
+          <t>78486</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19080</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30751</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41625</t>
+          <t>41816</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17484</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46302</t>
+          <t>46090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69924</t>
+          <t>69103</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73844</t>
+          <t>74216</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>94503</t>
+          <t>94832</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>72182</t>
+          <t>72415</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91928</t>
+          <t>91326</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>151296</t>
+          <t>152741</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>180573</t>
+          <t>180714</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>28730</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>29320</t>
+          <t>28371</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48225</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13002</t>
+          <t>12863</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24003</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>33022</t>
+          <t>32756</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43327</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>44385</t>
+          <t>44904</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>57647</t>
+          <t>57541</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>79444</t>
+          <t>81639</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>97109</t>
+          <t>98192</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19131</t>
+          <t>18584</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>56004</t>
+          <t>57084</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>37255</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>59286</t>
+          <t>59458</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>78355</t>
+          <t>76422</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>109345</t>
+          <t>107862</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>88809</t>
+          <t>89217</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>120089</t>
+          <t>120242</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>91998</t>
+          <t>91474</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>124088</t>
+          <t>121472</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>189387</t>
+          <t>191119</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>232634</t>
+          <t>232362</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>397494</t>
+          <t>395406</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>439595</t>
+          <t>438100</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>419652</t>
+          <t>420980</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>463619</t>
+          <t>461905</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>827819</t>
+          <t>830032</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>887150</t>
+          <t>892576</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,37%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>78401</t>
+          <t>78816</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>109132</t>
+          <t>108447</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>75082</t>
+          <t>75523</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>103280</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>164516</t>
+          <t>161820</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>204104</t>
+          <t>204588</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>35933</t>
+          <t>35605</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>31855</t>
+          <t>31742</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>53437</t>
+          <t>52663</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30110</t>
+          <t>30437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32390</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39436</t>
+          <t>38879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58168</t>
+          <t>59205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>25762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39642</t>
+          <t>40112</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>51972</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66725</t>
+          <t>65192</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87614</t>
+          <t>86504</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32026</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33573</t>
+          <t>33282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53026</t>
+          <t>52311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -11200,82 +11200,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5345</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>535</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5390</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>20343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27729</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>29897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>32733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52204</t>
+          <t>52517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>51502</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68852</t>
+          <t>68958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47695</t>
+          <t>47569</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65676</t>
+          <t>64168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104944</t>
+          <t>104710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129733</t>
+          <t>129093</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26584</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29826</t>
+          <t>29173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31665</t>
+          <t>32804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>51055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22462</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>22635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>36966</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28295</t>
+          <t>28581</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42638</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55360</t>
+          <t>55771</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75156</t>
+          <t>75810</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>30143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>759</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26589</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>25941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44584</t>
+          <t>43973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>48944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>69127</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>37970</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57770</t>
+          <t>58387</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>92088</t>
+          <t>93294</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>121806</t>
+          <t>121855</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91755</t>
+          <t>92339</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116078</t>
+          <t>116637</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94076</t>
+          <t>94287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118865</t>
+          <t>117469</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>193382</t>
+          <t>193109</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>227159</t>
+          <t>227248</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>24059</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>41412</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>28647</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>46046</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57341</t>
+          <t>56926</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83073</t>
+          <t>82268</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18677</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16372</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43614</t>
+          <t>43799</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>24582</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43350</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>57202</t>
+          <t>57843</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>81399</t>
+          <t>81154</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60569</t>
+          <t>61174</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>79060</t>
+          <t>79702</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>60281</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>81234</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>127486</t>
+          <t>124704</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>154715</t>
+          <t>154424</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26999</t>
+          <t>27256</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>32057</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>33607</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>53601</t>
+          <t>53987</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>29724</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>32299</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>51441</t>
+          <t>50492</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18550</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31575</t>
+          <t>30743</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>25639</t>
+          <t>25491</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>39482</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>48279</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>66091</t>
+          <t>66709</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>25108</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>38864</t>
+          <t>39088</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>61044</t>
+          <t>61190</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>39996</t>
+          <t>39875</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>62214</t>
+          <t>61347</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>85181</t>
+          <t>83724</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>114392</t>
+          <t>115029</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>150649</t>
+          <t>153299</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>187850</t>
+          <t>189018</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>150555</t>
+          <t>149667</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>186472</t>
+          <t>187385</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>312643</t>
+          <t>312571</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>362620</t>
+          <t>363352</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>300777</t>
+          <t>302887</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>343759</t>
+          <t>343627</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>322771</t>
+          <t>323341</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>365850</t>
+          <t>365739</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>636490</t>
+          <t>635139</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>698398</t>
+          <t>696804</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>92698</t>
+          <t>94550</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>123501</t>
+          <t>126119</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>111062</t>
+          <t>110893</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>147215</t>
+          <t>145607</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>214280</t>
+          <t>214713</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>260079</t>
+          <t>262231</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>26088</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>26391</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>46496</t>
+          <t>46575</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
